--- a/EXCEL/Exercise Files/Chapter04/04_02_Uniform.xlsx
+++ b/EXCEL/Exercise Files/Chapter04/04_02_Uniform.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD3ED78-C080-438F-8874-CD01A79DB2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E6B1F8-8757-4017-9397-DB4DFE1E413B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -390,58 +399,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E3">
+        <f>1/B5</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <f>1/B5+1/B5</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B5">
+        <f>B4-B3+1</f>
+        <v>6</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B7">
+        <f ca="1">RANDBETWEEN(B3,B4)</f>
+        <v>2</v>
+      </c>
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E7">
+        <f>1-E4</f>
+        <v>0.66666666666666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B8">
+        <f ca="1">RANDBETWEEN(B3,B4)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="B10">
+        <f ca="1">RAND()</f>
+        <v>0.95294250787439971</v>
       </c>
     </row>
   </sheetData>
